--- a/templates/quotation_template.xlsx
+++ b/templates/quotation_template.xlsx
@@ -9,7 +9,7 @@
     <sheet name="스토어 견적서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'스토어 견적서'!$A$1:$V$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'스토어 견적서'!$A$1:$V$29</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col width="0.375" customWidth="1" style="15" min="1" max="1"/>
@@ -1630,35 +1630,35 @@
     </row>
     <row r="27" ht="18" customHeight="1" s="74">
       <c r="A27" s="47" t="n"/>
-      <c r="B27" s="70" t="n"/>
-      <c r="C27" s="76" t="n"/>
-      <c r="D27" s="76" t="n"/>
-      <c r="E27" s="76" t="n"/>
-      <c r="F27" s="76" t="n"/>
-      <c r="G27" s="76" t="n"/>
-      <c r="H27" s="76" t="n"/>
-      <c r="I27" s="76" t="n"/>
-      <c r="J27" s="76" t="n"/>
-      <c r="K27" s="76" t="n"/>
-      <c r="L27" s="76" t="n"/>
-      <c r="M27" s="76" t="n"/>
-      <c r="N27" s="76" t="n"/>
-      <c r="O27" s="76" t="n"/>
-      <c r="P27" s="76" t="n"/>
-      <c r="Q27" s="76" t="n"/>
-      <c r="R27" s="76" t="n"/>
-      <c r="S27" s="76" t="n"/>
-      <c r="T27" s="76" t="n"/>
-      <c r="U27" s="76" t="n"/>
-      <c r="V27" s="76" t="n"/>
+      <c r="B27" s="71" t="inlineStr">
+        <is>
+          <t>결제 방법 :</t>
+        </is>
+      </c>
+      <c r="C27" s="75" t="n"/>
+      <c r="D27" s="75" t="n"/>
+      <c r="E27" s="75" t="n"/>
+      <c r="F27" s="75" t="n"/>
+      <c r="G27" s="75" t="n"/>
+      <c r="H27" s="75" t="n"/>
+      <c r="I27" s="75" t="n"/>
+      <c r="J27" s="75" t="n"/>
+      <c r="K27" s="75" t="n"/>
+      <c r="L27" s="75" t="n"/>
+      <c r="M27" s="75" t="n"/>
+      <c r="N27" s="75" t="n"/>
+      <c r="O27" s="75" t="n"/>
+      <c r="P27" s="75" t="n"/>
+      <c r="Q27" s="75" t="n"/>
+      <c r="R27" s="75" t="n"/>
+      <c r="S27" s="75" t="n"/>
+      <c r="T27" s="75" t="n"/>
+      <c r="U27" s="75" t="n"/>
+      <c r="V27" s="75" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="74">
       <c r="A28" s="47" t="n"/>
-      <c r="B28" s="71" t="inlineStr">
-        <is>
-          <t>결제 방법 : 직거래 구입</t>
-        </is>
-      </c>
+      <c r="B28" s="71" t="n"/>
       <c r="C28" s="75" t="n"/>
       <c r="D28" s="75" t="n"/>
       <c r="E28" s="75" t="n"/>
@@ -1680,56 +1680,32 @@
       <c r="U28" s="75" t="n"/>
       <c r="V28" s="75" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="74">
+    <row r="29" ht="3" customHeight="1" s="74">
       <c r="A29" s="47" t="n"/>
-      <c r="B29" s="71" t="n"/>
-      <c r="C29" s="75" t="n"/>
-      <c r="D29" s="75" t="n"/>
-      <c r="E29" s="75" t="n"/>
-      <c r="F29" s="75" t="n"/>
-      <c r="G29" s="75" t="n"/>
-      <c r="H29" s="75" t="n"/>
-      <c r="I29" s="75" t="n"/>
-      <c r="J29" s="75" t="n"/>
-      <c r="K29" s="75" t="n"/>
-      <c r="L29" s="75" t="n"/>
-      <c r="M29" s="75" t="n"/>
-      <c r="N29" s="75" t="n"/>
-      <c r="O29" s="75" t="n"/>
-      <c r="P29" s="75" t="n"/>
-      <c r="Q29" s="75" t="n"/>
-      <c r="R29" s="75" t="n"/>
-      <c r="S29" s="75" t="n"/>
-      <c r="T29" s="75" t="n"/>
-      <c r="U29" s="75" t="n"/>
-      <c r="V29" s="75" t="n"/>
-    </row>
-    <row r="30" ht="3" customHeight="1" s="74">
-      <c r="A30" s="47" t="n"/>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="17" t="n"/>
-      <c r="H30" s="17" t="n"/>
-      <c r="I30" s="17" t="n"/>
-      <c r="J30" s="17" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="17" t="n"/>
-      <c r="M30" s="17" t="n"/>
-      <c r="N30" s="17" t="n"/>
-      <c r="O30" s="17" t="n"/>
-      <c r="P30" s="17" t="n"/>
-      <c r="Q30" s="17" t="n"/>
-      <c r="R30" s="17" t="n"/>
-      <c r="S30" s="17" t="n"/>
-      <c r="T30" s="17" t="n"/>
-      <c r="U30" s="17" t="n"/>
-      <c r="V30" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+      <c r="M29" s="17" t="n"/>
+      <c r="N29" s="17" t="n"/>
+      <c r="O29" s="17" t="n"/>
+      <c r="P29" s="17" t="n"/>
+      <c r="Q29" s="17" t="n"/>
+      <c r="R29" s="17" t="n"/>
+      <c r="S29" s="17" t="n"/>
+      <c r="T29" s="17" t="n"/>
+      <c r="U29" s="17" t="n"/>
+      <c r="V29" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="65">
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="O7:P7"/>
     <mergeCell ref="R9:V11"/>
@@ -1755,7 +1731,6 @@
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="N19:P19"/>
-    <mergeCell ref="B29:V29"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="R22:T22"/>
     <mergeCell ref="R17:T17"/>
